--- a/kronshtatsky/floors/Наливной пол.xlsx
+++ b/kronshtatsky/floors/Наливной пол.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6924" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6924" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="1-Шл" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="1-Шл_ВОр" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="13">
   <si>
     <t>№ пом.</t>
   </si>
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -268,6 +268,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1481,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.109375" customWidth="1"/>
@@ -1584,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="10">
-        <v>63.6</v>
+        <v>63.3</v>
       </c>
       <c r="E4" s="11">
         <v>2.0299999999999998</v>
@@ -1613,7 +1619,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="12">
-        <v>63.7</v>
+        <v>63.4</v>
       </c>
       <c r="E5" s="9">
         <v>2.04</v>
@@ -1642,7 +1648,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="10">
-        <v>128.5</v>
+        <v>127.5</v>
       </c>
       <c r="E6" s="11">
         <v>2.0499999999999998</v>
@@ -1693,14 +1699,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="10">
-        <v>19.899999999999999</v>
+      <c r="A8" s="11">
+        <v>1.28</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12">
+        <v>21.6</v>
       </c>
       <c r="E8" s="11">
         <v>2.0699999999999998</v>
@@ -1723,13 +1729,13 @@
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="12">
-        <v>9.9</v>
+        <v>28.7</v>
       </c>
       <c r="E9" s="9">
         <v>2.08</v>
@@ -1738,7 +1744,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="10">
-        <v>77.8</v>
+        <v>76.8</v>
       </c>
       <c r="I9" s="9">
         <v>3.08</v>
@@ -1752,13 +1758,13 @@
     </row>
     <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="10">
-        <v>10.1</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E10" s="11">
         <v>2.12</v>
@@ -1776,18 +1782,18 @@
         <v>5</v>
       </c>
       <c r="K10" s="12">
-        <v>241.5</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="12">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
       <c r="E11" s="9">
         <v>2.15</v>
@@ -1810,22 +1816,22 @@
     </row>
     <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="10">
-        <v>25.3</v>
-      </c>
-      <c r="E12" s="11">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="12">
-        <v>30.8</v>
+        <v>50.7</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2.19</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="10">
+        <v>352.7</v>
       </c>
       <c r="I12" s="11">
         <v>3.18</v>
@@ -1839,22 +1845,22 @@
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="12">
-        <v>21.6</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.19</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="10">
-        <v>355.7</v>
+        <v>54.4</v>
+      </c>
+      <c r="E13" s="11">
+        <v>2.21</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12">
+        <v>13.7</v>
       </c>
       <c r="I13" s="9">
         <v>3.19</v>
@@ -1863,27 +1869,27 @@
         <v>3</v>
       </c>
       <c r="K13" s="10">
-        <v>111.4</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="10">
-        <v>91.2</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2.21</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="12">
-        <v>13.7</v>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2.27</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="10">
+        <v>18.7</v>
       </c>
       <c r="I14" s="11">
         <v>3.23</v>
@@ -1897,22 +1903,22 @@
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="12">
-        <v>111.8</v>
-      </c>
-      <c r="E15" s="9">
-        <v>2.27</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="10">
-        <v>18.7</v>
+        <v>50.6</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="12">
+        <v>189</v>
       </c>
       <c r="I15" s="9">
         <v>3.25</v>
@@ -1926,22 +1932,22 @@
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="10">
-        <v>9.1999999999999993</v>
+        <v>55.1</v>
       </c>
       <c r="E16" s="11">
-        <v>2.2799999999999998</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="12">
-        <v>189</v>
+        <v>112.3</v>
       </c>
       <c r="I16" s="11">
         <v>3.26</v>
@@ -1954,23 +1960,23 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
-        <v>1.58</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="12">
-        <v>58.3</v>
+      <c r="A17" s="21">
+        <v>1.77</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="22">
+        <v>40.299999999999997</v>
       </c>
       <c r="E17" s="9">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="10">
-        <v>14</v>
+        <v>21.1</v>
       </c>
       <c r="I17" s="9">
         <v>3.28</v>
@@ -1983,23 +1989,23 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>1.61</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="10">
-        <v>16.600000000000001</v>
+      <c r="A18" s="11">
+        <v>1.78</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="12">
+        <v>59.4</v>
       </c>
       <c r="E18" s="11">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="12">
-        <v>114.3</v>
+        <v>50.2</v>
       </c>
       <c r="I18" s="11">
         <v>3.29</v>
@@ -2012,23 +2018,22 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
-        <v>1.64</v>
-      </c>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="13"/>
+      <c r="B19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="13">
+        <f>SUM(C2:C18)</f>
+        <v>777.6</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2.41</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="12">
-        <v>23.5</v>
-      </c>
-      <c r="E19" s="9">
-        <v>2.37</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>5</v>
-      </c>
       <c r="G19" s="10">
-        <v>21.1</v>
+        <v>56</v>
       </c>
       <c r="I19" s="9">
         <v>3.3</v>
@@ -2041,23 +2046,14 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>1.67</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="10">
-        <v>50.7</v>
-      </c>
       <c r="E20" s="11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="12">
-        <v>50.2</v>
+        <v>21.2</v>
       </c>
       <c r="I20" s="11">
         <v>3.33</v>
@@ -2070,23 +2066,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
-        <v>1.68</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="12">
-        <v>55.4</v>
-      </c>
       <c r="E21" s="9">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="10">
-        <v>56</v>
+        <v>50.2</v>
       </c>
       <c r="I21" s="9">
         <v>3.34</v>
@@ -2099,23 +2086,14 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
-        <v>1.69</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="E22" s="11">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="10">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="E22" s="11">
-        <v>2.42</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>5</v>
-      </c>
       <c r="G22" s="12">
-        <v>21.2</v>
+        <v>55.1</v>
       </c>
       <c r="I22" s="11">
         <v>3.35</v>
@@ -2128,23 +2106,14 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="11">
-        <v>1.73</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="12">
-        <v>50.6</v>
-      </c>
       <c r="E23" s="9">
-        <v>2.44</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="10">
-        <v>50.2</v>
+        <v>73.8</v>
       </c>
       <c r="I23" s="9">
         <v>3.41</v>
@@ -2157,23 +2126,14 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
-        <v>1.74</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="10">
-        <v>55.1</v>
-      </c>
       <c r="E24" s="11">
-        <v>2.4500000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="12">
-        <v>55.1</v>
+        <v>6.8</v>
       </c>
       <c r="I24" s="11">
         <v>3.42</v>
@@ -2186,23 +2146,14 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
-        <v>1.76</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="12">
-        <v>6.2</v>
-      </c>
       <c r="E25" s="9">
-        <v>2.4700000000000002</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="10">
-        <v>74.8</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="I25" s="9">
         <v>3.44</v>
@@ -2215,23 +2166,14 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9">
-        <v>1.77</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="10">
-        <v>40.299999999999997</v>
-      </c>
       <c r="E26" s="11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="12">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="I26" s="11">
         <v>3.45</v>
@@ -2244,23 +2186,14 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11">
-        <v>1.78</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="12">
-        <v>59.4</v>
-      </c>
       <c r="E27" s="9">
-        <v>2.4900000000000002</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="10">
-        <v>73.599999999999994</v>
+        <v>37.9</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="10" t="s">
@@ -2268,82 +2201,44 @@
       </c>
       <c r="K27" s="13">
         <f>SUM(K2:K26)</f>
-        <v>1574.8999999999994</v>
+        <v>1571.8999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="9">
-        <v>1.82</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="10">
-        <v>24</v>
-      </c>
       <c r="E28" s="11">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="12">
-        <v>6.1</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="10" t="s">
+      <c r="E29" s="9">
+        <v>2.58</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="10">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E30" s="13"/>
+      <c r="F30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="13">
-        <f>SUM(C2:C28)</f>
-        <v>1127.9000000000003</v>
-      </c>
-      <c r="E29" s="9">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="10">
-        <v>37.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E30" s="11">
-        <v>2.56</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="G30" s="12">
-        <v>62.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E31" s="9">
-        <v>2.58</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G31" s="10">
-        <v>74.599999999999994</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E32" s="13"/>
-      <c r="F32" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="13">
-        <f>SUM(G2:G31)</f>
-        <v>1895.8999999999999</v>
+      <c r="G30" s="13">
+        <f>SUM(G2:G29)</f>
+        <v>1844.1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2379,8 +2274,8 @@
         <v>11</v>
       </c>
       <c r="C3" s="19">
-        <f>'1-Шл'!C29+'1-Шл'!G32+'1-Шл'!K27</f>
-        <v>4598.7</v>
+        <f>'1-Шл'!C19+'1-Шл'!G30+'1-Шл'!K27</f>
+        <v>4193.5999999999995</v>
       </c>
     </row>
   </sheetData>
